--- a/site/Monday-com-Okta-Integration-Guide/headings.xlsx
+++ b/site/Monday-com-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,51 +771,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User Provisioning</t>
+          <t>Pre-Transaction Email Notification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KRZTD75QAMT5Z649EJBGF5NF</t>
+          <t>h_01KS1T07RQ8663MGS50GTDB080</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTD75QAMT5Z649EJBGF5NF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS1T07RQ8663MGS50GTDB080</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KRZTDHC096VZV5K63R70WY5R</t>
+          <t>h_01KS1T1AMZSN31XFK9KG0SR7F8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDHC096VZV5K63R70WY5R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS1T1AMZSN31XFK9KG0SR7F8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>User Provisioning</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,32 +825,76 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>h_01KRZTD75QAMT5Z649EJBGF5NF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTD75QAMT5Z649EJBGF5NF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KRZTDHC096VZV5K63R70WY5R</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDHC096VZV5K63R70WY5R</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
         </is>

--- a/site/Monday-com-Okta-Integration-Guide/headings.xlsx
+++ b/site/Monday-com-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pre-Transaction Email Notification</t>
+          <t>Per-Transaction Email Notification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,29 +793,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>User Provisioning</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KS1T1AMZSN31XFK9KG0SR7F8</t>
+          <t>h_01KRZTD75QAMT5Z649EJBGF5NF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS1T1AMZSN31XFK9KG0SR7F8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTD75QAMT5Z649EJBGF5NF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>User Provisioning</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRZTD75QAMT5Z649EJBGF5NF</t>
+          <t>h_01KRZTDHC096VZV5K63R70WY5R</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTD75QAMT5Z649EJBGF5NF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDHC096VZV5K63R70WY5R</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KRZTDHC096VZV5K63R70WY5R</t>
+          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDHC096VZV5K63R70WY5R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,32 +869,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
         </is>

--- a/site/Monday-com-Okta-Integration-Guide/headings.xlsx
+++ b/site/Monday-com-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -837,44 +837,132 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Okta Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>h_01KS2CY5VT92493DXMQ3WRQVH0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS2CY5VT92493DXMQ3WRQVH0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Okta Attributes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KS2CZVKHECJKYKPBJAVJBMGQ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS2CZVKHECJKYKPBJAVJBMGQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/Monday-com-Okta-Integration-Guide/headings.xlsx
+++ b/site/Monday-com-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Per-Transaction Email Notification</t>
+          <t>Create Notification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,129 +781,129 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KS1T07RQ8663MGS50GTDB080</t>
+          <t>h_01KWBYX3F0RTA61SH30GBR24XY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS1T07RQ8663MGS50GTDB080</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWBYX3F0RTA61SH30GBR24XY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>User Provisioning</t>
+          <t>Update Notification</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KRZTD75QAMT5Z649EJBGF5NF</t>
+          <t>h_01KWC0ZPZ2H75MNTD0QVBRFMTW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTD75QAMT5Z649EJBGF5NF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWC0ZPZ2H75MNTD0QVBRFMTW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Deactivate Notification</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRZTDHC096VZV5K63R70WY5R</t>
+          <t>h_01KWC14AKM7Q185RPT9GF9K4JY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDHC096VZV5K63R70WY5R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWC14AKM7Q185RPT9GF9K4JY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Okta Configuration</t>
+          <t>User Provisioning</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KS2CY5VT92493DXMQ3WRQVH0</t>
+          <t>h_01KRZTD75QAMT5Z649EJBGF5NF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS2CY5VT92493DXMQ3WRQVH0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTD75QAMT5Z649EJBGF5NF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Okta Attributes</t>
+          <t>Select Source Application</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KS2CZVKHECJKYKPBJAVJBMGQ</t>
+          <t>h_01KWBX8JACJW35MSMS3BKXZGWX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS2CZVKHECJKYKPBJAVJBMGQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWBX8JACJW35MSMS3BKXZGWX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Board and Source Filter</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>h_01KWBX92WYN7ANMPE1SKZD64NP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWBX92WYN7ANMPE1SKZD64NP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,54 +913,186 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
+          <t>h_01KRZTDHC096VZV5K63R70WY5R</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDHC096VZV5K63R70WY5R</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Okta Configuration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KS2CY5VT92493DXMQ3WRQVH0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS2CY5VT92493DXMQ3WRQVH0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Okta Attributes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KS2CZVKHECJKYKPBJAVJBMGQ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KS2CZVKHECJKYKPBJAVJBMGQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KWC50ENTHCFZD974QN4MWXNE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWC50ENTHCFZD974QN4MWXNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unique Identity</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KWC56W7HSKE87AK2MPY0WQ9X</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KWC56W7HSKE87AK2MPY0WQ9X</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KRZTDV927F8X8N25KP5JEK1S</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTDV927F8X8N25KP5JEK1S</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01KRZTE4SPAYYR9RAC72MRTFHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Monday-com-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
